--- a/Actions.xlsx
+++ b/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\1  Universidad\Compiladores\ProyectoCompiladores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1E6CF2-57B3-4F38-9A9D-9358D1B1FF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C0F819-363D-4F23-9141-391C0FB1509F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="3444" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="No Terminales" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="424">
   <si>
     <t>Estado</t>
   </si>
@@ -1272,6 +1272,63 @@
   </si>
   <si>
     <t>Accion sintactica</t>
+  </si>
+  <si>
+    <t>'='</t>
+  </si>
+  <si>
+    <t>'&lt;&gt;'</t>
+  </si>
+  <si>
+    <t>'&lt;'</t>
+  </si>
+  <si>
+    <t>'&lt;='</t>
+  </si>
+  <si>
+    <t>'&gt;'</t>
+  </si>
+  <si>
+    <t>'&gt;='</t>
+  </si>
+  <si>
+    <t>'+'</t>
+  </si>
+  <si>
+    <t>'-'</t>
+  </si>
+  <si>
+    <t>'OR'</t>
+  </si>
+  <si>
+    <t>'*'</t>
+  </si>
+  <si>
+    <t>'/'</t>
+  </si>
+  <si>
+    <t>'AND'</t>
+  </si>
+  <si>
+    <t>'TRUE'</t>
+  </si>
+  <si>
+    <t>'FALSE'</t>
+  </si>
+  <si>
+    <t>'"' str '"'</t>
+  </si>
+  <si>
+    <t>'INTEGER'</t>
+  </si>
+  <si>
+    <t>'REAL'</t>
+  </si>
+  <si>
+    <t>BOOLEAN'</t>
+  </si>
+  <si>
+    <t>'STRING'</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1341,6 +1398,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17863,12 +17921,12 @@
     <col min="2" max="2" width="21.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="52.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="7.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="105.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="105.140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -17951,7 +18009,7 @@
         <v>2</v>
       </c>
       <c r="J3" s="2" t="str">
-        <f t="shared" ref="J3:J66" si="3">_xlfn.CONCAT("&lt;",B3,"&gt; = ",C3," {",D3,"}")</f>
+        <f t="shared" ref="J3:J65" si="3">_xlfn.CONCAT("&lt;",B3,"&gt; = ",C3," {",D3,"}")</f>
         <v>&lt;block&gt; = &lt;declarations&gt; &lt;compound_statement&gt; {save_block}</v>
       </c>
       <c r="K3" s="2" t="str">
@@ -18269,8 +18327,8 @@
       <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
+      <c r="C13" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>377</v>
@@ -18288,7 +18346,7 @@
       </c>
       <c r="J13" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;type&gt; = INTEGER {save_type}</v>
+        <v>&lt;type&gt; = 'INTEGER' {save_type}</v>
       </c>
       <c r="K13" s="2" t="str">
         <f t="shared" si="4"/>
@@ -18302,8 +18360,8 @@
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>44</v>
+      <c r="C14" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>377</v>
@@ -18321,7 +18379,7 @@
       </c>
       <c r="J14" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;type&gt; = REAL {save_type}</v>
+        <v>&lt;type&gt; = 'REAL' {save_type}</v>
       </c>
       <c r="K14" s="2" t="str">
         <f t="shared" si="4"/>
@@ -18335,8 +18393,8 @@
       <c r="B15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
+      <c r="C15" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>377</v>
@@ -18354,7 +18412,7 @@
       </c>
       <c r="J15" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;type&gt; = BOOLEAN {save_type}</v>
+        <v>&lt;type&gt; = BOOLEAN' {save_type}</v>
       </c>
       <c r="K15" s="2" t="str">
         <f t="shared" si="4"/>
@@ -18368,8 +18426,8 @@
       <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>46</v>
+      <c r="C16" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>377</v>
@@ -18387,7 +18445,7 @@
       </c>
       <c r="J16" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;type&gt; = STRING {save_type}</v>
+        <v>&lt;type&gt; = 'STRING' {save_type}</v>
       </c>
       <c r="K16" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19408,7 +19466,7 @@
       </c>
       <c r="E49" s="2" t="str">
         <f>_xlfn.CONCAT(C63,",",C64)</f>
-        <v>TRUE,FALSE</v>
+        <v>'TRUE','FALSE'</v>
       </c>
       <c r="F49" s="4">
         <f t="shared" si="1"/>
@@ -19459,15 +19517,15 @@
       <c r="B51" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>52</v>
+      <c r="C51" s="5" t="s">
+        <v>405</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E51" s="2" t="str">
         <f t="shared" ref="E51:E65" si="11">C51</f>
-        <v>=</v>
+        <v>'='</v>
       </c>
       <c r="F51" s="4">
         <f t="shared" si="1"/>
@@ -19475,7 +19533,7 @@
       </c>
       <c r="J51" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;relational_operator&gt; = = {save_operator}</v>
+        <v>&lt;relational_operator&gt; = '=' {save_operator}</v>
       </c>
       <c r="K51" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19489,15 +19547,15 @@
       <c r="B52" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>340</v>
+      <c r="C52" s="5" t="s">
+        <v>406</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E52" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>&lt;&gt;</v>
+        <v>'&lt;&gt;'</v>
       </c>
       <c r="F52" s="4">
         <f t="shared" si="1"/>
@@ -19505,7 +19563,7 @@
       </c>
       <c r="J52" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;relational_operator&gt; = &lt;&gt; {save_operator}</v>
+        <v>&lt;relational_operator&gt; = '&lt;&gt;' {save_operator}</v>
       </c>
       <c r="K52" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19519,15 +19577,15 @@
       <c r="B53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>339</v>
+      <c r="C53" s="5" t="s">
+        <v>407</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E53" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>&lt;</v>
+        <v>'&lt;'</v>
       </c>
       <c r="F53" s="4">
         <f t="shared" si="1"/>
@@ -19535,7 +19593,7 @@
       </c>
       <c r="J53" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;relational_operator&gt; = &lt; {save_operator}</v>
+        <v>&lt;relational_operator&gt; = '&lt;' {save_operator}</v>
       </c>
       <c r="K53" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19549,15 +19607,15 @@
       <c r="B54" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>338</v>
+      <c r="C54" s="5" t="s">
+        <v>408</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E54" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>&lt;=</v>
+        <v>'&lt;='</v>
       </c>
       <c r="F54" s="4">
         <f t="shared" si="1"/>
@@ -19565,7 +19623,7 @@
       </c>
       <c r="J54" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;relational_operator&gt; = &lt;= {save_operator}</v>
+        <v>&lt;relational_operator&gt; = '&lt;=' {save_operator}</v>
       </c>
       <c r="K54" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19579,15 +19637,15 @@
       <c r="B55" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>337</v>
+      <c r="C55" s="5" t="s">
+        <v>409</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E55" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>&gt;</v>
+        <v>'&gt;'</v>
       </c>
       <c r="F55" s="4">
         <f t="shared" si="1"/>
@@ -19595,7 +19653,7 @@
       </c>
       <c r="J55" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;relational_operator&gt; = &gt; {save_operator}</v>
+        <v>&lt;relational_operator&gt; = '&gt;' {save_operator}</v>
       </c>
       <c r="K55" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19609,15 +19667,15 @@
       <c r="B56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>336</v>
+      <c r="C56" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E56" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>&gt;=</v>
+        <v>'&gt;='</v>
       </c>
       <c r="F56" s="4">
         <f t="shared" si="1"/>
@@ -19625,7 +19683,7 @@
       </c>
       <c r="J56" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;relational_operator&gt; = &gt;= {save_operator}</v>
+        <v>&lt;relational_operator&gt; = '&gt;=' {save_operator}</v>
       </c>
       <c r="K56" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19639,15 +19697,15 @@
       <c r="B57" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>54</v>
+      <c r="C57" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E57" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>+</v>
+        <v>'+'</v>
       </c>
       <c r="F57" s="4">
         <f t="shared" si="1"/>
@@ -19655,7 +19713,7 @@
       </c>
       <c r="J57" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;additive_operator&gt; = + {save_operator}</v>
+        <v>&lt;additive_operator&gt; = '+' {save_operator}</v>
       </c>
       <c r="K57" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19669,15 +19727,15 @@
       <c r="B58" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>55</v>
+      <c r="C58" s="5" t="s">
+        <v>412</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E58" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>-</v>
+        <v>'-'</v>
       </c>
       <c r="F58" s="4">
         <f t="shared" si="1"/>
@@ -19685,7 +19743,7 @@
       </c>
       <c r="J58" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;additive_operator&gt; = - {save_operator}</v>
+        <v>&lt;additive_operator&gt; = '-' {save_operator}</v>
       </c>
       <c r="K58" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19699,15 +19757,15 @@
       <c r="B59" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>56</v>
+      <c r="C59" s="5" t="s">
+        <v>413</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E59" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>OR</v>
+        <v>'OR'</v>
       </c>
       <c r="F59" s="4">
         <f t="shared" si="1"/>
@@ -19715,7 +19773,7 @@
       </c>
       <c r="J59" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;additive_operator&gt; = OR {save_operator}</v>
+        <v>&lt;additive_operator&gt; = 'OR' {save_operator}</v>
       </c>
       <c r="K59" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19729,15 +19787,15 @@
       <c r="B60" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>58</v>
+      <c r="C60" s="5" t="s">
+        <v>414</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E60" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>*</v>
+        <v>'*'</v>
       </c>
       <c r="F60" s="4">
         <f t="shared" si="1"/>
@@ -19745,7 +19803,7 @@
       </c>
       <c r="J60" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;multiplicative_operator&gt; = * {save_operator}</v>
+        <v>&lt;multiplicative_operator&gt; = '*' {save_operator}</v>
       </c>
       <c r="K60" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19759,15 +19817,15 @@
       <c r="B61" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>59</v>
+      <c r="C61" s="5" t="s">
+        <v>415</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E61" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>/</v>
+        <v>'/'</v>
       </c>
       <c r="F61" s="4">
         <f t="shared" si="1"/>
@@ -19775,7 +19833,7 @@
       </c>
       <c r="J61" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;multiplicative_operator&gt; = / {save_operator}</v>
+        <v>&lt;multiplicative_operator&gt; = '/' {save_operator}</v>
       </c>
       <c r="K61" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19789,15 +19847,15 @@
       <c r="B62" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>60</v>
+      <c r="C62" s="5" t="s">
+        <v>416</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>385</v>
       </c>
       <c r="E62" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>AND</v>
+        <v>'AND'</v>
       </c>
       <c r="F62" s="4">
         <f t="shared" si="1"/>
@@ -19805,7 +19863,7 @@
       </c>
       <c r="J62" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;multiplicative_operator&gt; = AND {save_operator}</v>
+        <v>&lt;multiplicative_operator&gt; = 'AND' {save_operator}</v>
       </c>
       <c r="K62" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19819,15 +19877,15 @@
       <c r="B63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>39</v>
+      <c r="C63" s="5" t="s">
+        <v>417</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>386</v>
       </c>
       <c r="E63" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>TRUE</v>
+        <v>'TRUE'</v>
       </c>
       <c r="F63" s="4">
         <f t="shared" si="1"/>
@@ -19835,7 +19893,7 @@
       </c>
       <c r="J63" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;boolean_constant&gt; = TRUE {save_boolean}</v>
+        <v>&lt;boolean_constant&gt; = 'TRUE' {save_boolean}</v>
       </c>
       <c r="K63" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19849,15 +19907,15 @@
       <c r="B64" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>40</v>
+      <c r="C64" s="5" t="s">
+        <v>418</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>386</v>
       </c>
       <c r="E64" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>FALSE</v>
+        <v>'FALSE'</v>
       </c>
       <c r="F64" s="4">
         <f t="shared" si="1"/>
@@ -19865,7 +19923,7 @@
       </c>
       <c r="J64" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;boolean_constant&gt; = FALSE {save_boolean}</v>
+        <v>&lt;boolean_constant&gt; = 'FALSE' {save_boolean}</v>
       </c>
       <c r="K64" s="2" t="str">
         <f t="shared" si="4"/>
@@ -19879,15 +19937,15 @@
       <c r="B65" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>335</v>
+      <c r="C65" s="5" t="s">
+        <v>419</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E65" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>"' str '"</v>
+        <v>'"' str '"'</v>
       </c>
       <c r="F65" s="4">
         <f t="shared" si="1"/>
@@ -19895,7 +19953,7 @@
       </c>
       <c r="J65" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;string_constant&gt; = "' str '" {save_string}</v>
+        <v>&lt;string_constant&gt; = '"' str '"' {save_string}</v>
       </c>
       <c r="K65" s="2" t="str">
         <f t="shared" si="4"/>
